--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -934,7 +934,13 @@
         <v>COE certificado</v>
       </c>
       <c r="D29" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F29" s="1" t="str">
+        <v>13/09/2026</v>
+      </c>
+      <c r="G29" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=HwLWxUHl_7I | Short: https://www.youtube.com/watch?v=dlY1KBCb1HM</v>
       </c>
       <c r="I29" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3596,7 +3596,13 @@
         <v>desconto a vista</v>
       </c>
       <c r="D175" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F175" s="1" t="str">
+        <v>14/09/2026</v>
+      </c>
+      <c r="G175" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=nH941kgTKGI | Short: https://www.youtube.com/watch?v=5uOWxdYgVEY</v>
       </c>
       <c r="I175" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2191,7 +2191,13 @@
         <v>open finance</v>
       </c>
       <c r="D98" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F98" s="1" t="str">
+        <v>15/09/2026</v>
+      </c>
+      <c r="G98" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=u175-iw0se0 | Short: https://www.youtube.com/watch?v=gF1YxrgL-Y0</v>
       </c>
       <c r="I98" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3324,7 +3324,13 @@
         <v>feirao limpa nome</v>
       </c>
       <c r="D159" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F159" s="1" t="str">
+        <v>16/09/2026</v>
+      </c>
+      <c r="G159" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=YSwHa21tuLw | Short: https://www.youtube.com/watch?v=XObwDyHk6KQ</v>
       </c>
       <c r="I159" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -547,7 +547,13 @@
         <v>seguro cartao</v>
       </c>
       <c r="D8" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F8" s="1" t="str">
+        <v>17/09/2026</v>
+      </c>
+      <c r="G8" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=ffrJMBvHLuc | Short: https://www.youtube.com/watch?v=2L-gFiQkyic</v>
       </c>
       <c r="I8" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1930,7 +1930,13 @@
         <v>rotativo cartao</v>
       </c>
       <c r="D83" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F83" s="1" t="str">
+        <v>18/09/2026</v>
+      </c>
+      <c r="G83" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=lJifXQcx5Kg | Short: https://www.youtube.com/watch?v=eGXcpbyko2g</v>
       </c>
       <c r="I83" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -4514,7 +4514,13 @@
         <v>reserva automatica</v>
       </c>
       <c r="D223" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F223" s="1" t="str">
+        <v>19/09/2026</v>
+      </c>
+      <c r="G223" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=20KqfH86w2k | Short: https://www.youtube.com/watch?v=iR4iJeTnPqQ</v>
       </c>
       <c r="I223" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3603,7 +3603,13 @@
         <v>seguro de vida barato</v>
       </c>
       <c r="D174" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F174" s="1" t="str">
+        <v>20/09/2026</v>
+      </c>
+      <c r="G174" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=vPewxEPDQlA | Short: https://www.youtube.com/watch?v=qHoV52AUdrU</v>
       </c>
       <c r="I174" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2226,7 +2226,13 @@
         <v>come cotas</v>
       </c>
       <c r="D99" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F99" s="1" t="str">
+        <v>21/09/2026</v>
+      </c>
+      <c r="G99" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=XhsCFHKS8OE | Short: https://www.youtube.com/watch?v=FNanAdRsskM</v>
       </c>
       <c r="I99" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1913,7 +1913,13 @@
         <v>analise de credito</v>
       </c>
       <c r="D82" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F82" s="1" t="str">
+        <v>22/09/2026</v>
+      </c>
+      <c r="G82" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=gLLHxsjc7wU | Short: https://www.youtube.com/watch?v=8Q6olUuBL98</v>
       </c>
       <c r="I82" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1742,7 +1742,13 @@
         <v>emprestimo rapido</v>
       </c>
       <c r="D73" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F73" s="1" t="str">
+        <v>23/09/2026</v>
+      </c>
+      <c r="G73" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=wDj0xZcBSoY | Short: https://www.youtube.com/watch?v=0EqnDtPulIE</v>
       </c>
       <c r="I73" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3206,7 +3206,13 @@
         <v>reajuste plano de saude</v>
       </c>
       <c r="D151" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F151" s="1" t="str">
+        <v>24/09/2026</v>
+      </c>
+      <c r="G151" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=bEQ1PgHl4yY | Short: https://www.youtube.com/watch?v=TI41jNjE5GY</v>
       </c>
       <c r="I151" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -4704,7 +4704,13 @@
         <v>fintech predatoria</v>
       </c>
       <c r="D231" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F231" s="1" t="str">
+        <v>25/09/2026</v>
+      </c>
+      <c r="G231" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=8zvNKLxEQmQ | Short: https://www.youtube.com/watch?v=CZQnWB-fw1M</v>
       </c>
       <c r="I231" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -5335,7 +5335,13 @@
         <v>multinivel disfarcado</v>
       </c>
       <c r="D266" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F266" s="1" t="str">
+        <v>26/09/2026</v>
+      </c>
+      <c r="G266" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=ePOkzHOrFgA | Short: https://www.youtube.com/watch?v=9foSmxmgwTU</v>
       </c>
       <c r="I266" s="1" t="str">
         <v>Pirita</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -4236,7 +4236,13 @@
         <v>economizar supermercado</v>
       </c>
       <c r="D207" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F207" s="1" t="str">
+        <v>27/09/2026</v>
+      </c>
+      <c r="G207" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=C7RmNXLB7e0 | Short: https://www.youtube.com/watch?v=uLQasjuOOlA</v>
       </c>
       <c r="I207" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2614,7 +2614,13 @@
         <v>intercambio cartao</v>
       </c>
       <c r="D119" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F119" s="1" t="str">
+        <v>28/09/2026</v>
+      </c>
+      <c r="G119" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=p4p0beITznw | Short: https://www.youtube.com/watch?v=3GqJWtM4vPY</v>
       </c>
       <c r="I119" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3087,7 +3087,13 @@
         <v>banco central juros</v>
       </c>
       <c r="D144" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F144" s="1" t="str">
+        <v>29/09/2026</v>
+      </c>
+      <c r="G144" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=rIxBsjpK1qU | Short: https://www.youtube.com/watch?v=yPB-jcAjz_k</v>
       </c>
       <c r="I144" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -4682,7 +4682,13 @@
         <v>ler cet contrato</v>
       </c>
       <c r="D229" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F229" s="1" t="str">
+        <v>30/09/2026</v>
+      </c>
+      <c r="G229" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=H2gFYhtpxlo | Short: https://www.youtube.com/watch?v=zPHxe2ctUHU</v>
       </c>
       <c r="I229" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3861,7 +3861,13 @@
         <v>economizar mercado</v>
       </c>
       <c r="D186" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F186" s="1" t="str">
+        <v>01/10/2026</v>
+      </c>
+      <c r="G186" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=dJ_XDiFdwuE | Short: https://www.youtube.com/watch?v=C3V1U0hF8QQ</v>
       </c>
       <c r="I186" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2916,7 +2916,13 @@
         <v>prescricao de divida</v>
       </c>
       <c r="D135" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F135" s="1" t="str">
+        <v>02/10/2026</v>
+      </c>
+      <c r="G135" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=Y-I5IeEptbc | Short: https://www.youtube.com/watch?v=zs4Gy96tWOY</v>
       </c>
       <c r="I135" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3543,7 +3543,13 @@
         <v>investir 100 reais</v>
       </c>
       <c r="D168" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F168" s="1" t="str">
+        <v>03/10/2026</v>
+      </c>
+      <c r="G168" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=2vRizCWIm5s | Short: https://www.youtube.com/watch?v=14wQUo4LiVQ</v>
       </c>
       <c r="I168" s="1" t="str">
         <v>Ouro</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1902,7 +1902,13 @@
         <v>score nao sobe</v>
       </c>
       <c r="D81" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F81" s="1" t="str">
+        <v>04/10/2026</v>
+      </c>
+      <c r="G81" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=PU_rzpTBnU8 | Short: https://www.youtube.com/watch?v=IHr-n8SE4xE</v>
       </c>
       <c r="I81" s="1" t="str">
         <v>Misto</v>

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1623,7 +1623,13 @@
         <v>renda extra golpe</v>
       </c>
       <c r="D66" s="1" t="str">
-        <v>fila</v>
+        <v>publicado</v>
+      </c>
+      <c r="F66" s="1" t="str">
+        <v>06/10/2026</v>
+      </c>
+      <c r="G66" s="1" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=ZcQFsX7nySg | Short: https://www.youtube.com/watch?v=Q7EYEReivBk</v>
       </c>
       <c r="I66" s="1" t="str">
         <v>Pirita</v>
